--- a/product_surveys/042_product_quality_score_request_form--product_surveys.xlsx
+++ b/product_surveys/042_product_quality_score_request_form--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'mobile',_'label':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Mobile', 'label': 'Mobile'}</t>
+          <t>Mobile</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'laptops',_'label':_'laptops'}</t>
+          <t>laptops</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Laptops', 'label': 'Laptops'}</t>
+          <t>Laptops</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'tablets',_'label':_'tablets'}</t>
+          <t>tablets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Tablets', 'label': 'Tablets'}</t>
+          <t>Tablets</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'desktop',_'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Desktop', 'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'wearable',_'label':_'wearable'}</t>
+          <t>wearable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Wearable', 'label': 'Wearable'}</t>
+          <t>Wearable</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'gaming_console',_'label':_'gaming_console'}</t>
+          <t>gaming_console</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Gaming Console', 'label': 'Gaming Console'}</t>
+          <t>Gaming Console</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'windows',_'label':_'windows'}</t>
+          <t>windows</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'windows', 'label': 'Windows'}</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'mac',_'label':_'mac'}</t>
+          <t>mac</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'mac', 'label': 'Mac'}</t>
+          <t>Mac</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'android',_'label':_'android'}</t>
+          <t>android</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'android', 'label': 'Android'}</t>
+          <t>Android</t>
         </is>
       </c>
     </row>
